--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0006.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0006.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Tăng 50% tỉ lệ rơi Shell Credit trong 3 giờ. Chỉ có hiệu lực với Cộng Hưởng Giả của chính bạn trong Chế Độ Hợp Tác.</t>
+          <t>Tăng 50% tỉ lệ rơi Shell Credit trong 3 giờ. Chỉ có hiệu lực với Resonator của chính bạn trong Chế Độ Hợp Tác.</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Tăng tỷ lệ rơi Echo lên 50% trong 3 giờ. Chỉ có hiệu lực với Cộng Hưởng Giả của chính bạn trong Chế Độ Hợp Tác.</t>
+          <t>Tăng tỷ lệ rơi Echo lên 50% trong 3 giờ. Chỉ có hiệu lực với Resonator của chính bạn trong Chế Độ Hợp Tác.</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Tăng tỷ lệ rơi Echo lên 50% trong 3 giờ. Chỉ có hiệu lực với Cộng Hưởng Giả của chính bạn trong Chế Độ Hợp Tác.</t>
+          <t>Tăng tỷ lệ rơi Echo lên 50% trong 3 giờ. Chỉ có hiệu lực với Resonator của chính bạn trong Chế Độ Hợp Tác.</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Trăng khuyết tròn in cành lá. Ánh sáng bóng tối lướt sương mai.</t>
+          <t>Thịnh suy khắc cành. Sáng tối lướt giọt sương.</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Vầng trăng ban cho bạn sự khai sáng và phước lành.</t>
+          <t>Vầng trăng ban cho ngươi sự khai sáng và phước lành.</t>
         </is>
       </c>
     </row>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Varr đang ngươi mò tìm ý tưởng cho một cuốn tiểu thuyết hấp dẫn. Nguồn cảm hứng của cậu chủ yếu đến từ truyền thuyết về Exostrider.</t>
+          <t>Varr đang mày mò tìm ý tưởng cho một cuốn tiểu thuyết hấp dẫn. Nguồn cảm hứng của cậu chủ yếu đến từ truyền thuyết về Exostrider.</t>
         </is>
       </c>
     </row>
@@ -5981,7 +5981,7 @@
       <c r="M85" t="inlineStr">
         <is>
           <t>- Giai đoạn nơi các Echo giao đấu với nhau.
-- {Cus:Ipt,Touch=tap PC=click Gamepad=press} "Chiến đấu!" để vào giai đoạn này.</t>
+- {Cus:Ipt,Touch=Tap PC=Click Gamepad=Press} "Chiến đấu!" để vào giai đoạn này.</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Chọn một bộ Chiến Thuật Cộng Hưởng Giả và mang theo bộ bài đầy đủ trước khi bắt đầu trận đấu.</t>
+          <t>Chọn một bộ Chiến Thuật Resonator và mang theo bộ bài đầy đủ trước khi bắt đầu trận đấu.</t>
         </is>
       </c>
     </row>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Có thể nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Khảo Sát Vùng Biển Sâu."
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Có thể nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Khảo Sát Vùng Biển Sâu."
 Sự sống có thể phai nhạt, tan biến thành những con sóng vô hình.</t>
         </is>
       </c>
@@ -6959,7 +6959,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Có thể nhận sau khi hoàn thành Nhiệm Vụ Phụ "Khảo sát Vực Sâu."
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Có thể nhận sau khi hoàn thành Nhiệm Vụ Phụ "Khảo sát Vực Sâu."
 Sự sống có thể được tạo ra, tái dựng đôi tay của sự phục tùng.</t>
         </is>
       </c>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Có thể nhận sau khi hoàn thành Nhiệm Vụ Phụ "Khảo sát Vực Sâu."
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Có thể nhận sau khi hoàn thành Nhiệm Vụ Phụ "Khảo sát Vực Sâu."
 Sự sống có thể được tích tụ, hội tụ thành nguồn tái sinh.</t>
         </is>
       </c>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Có thể nhận sau khi hoàn thành Nhiệm Vụ Phụ "Khảo sát Vực Sâu."
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Có thể nhận sau khi hoàn thành Nhiệm Vụ Phụ "Khảo sát Vực Sâu."
 Sự sống có thể là vĩnh cửu, gìn giữ hơi ấm của quá khứ.</t>
         </is>
       </c>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Có thể nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Khảo Sát Vùng Biển Sâu."
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Có thể nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Khảo Sát Vùng Biển Sâu."
 Sự sống có thể thuần khiết, dệt nên bản giao hưởng của lòng dũng cảm.</t>
         </is>
       </c>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Có thể nhận sau khi hoàn thành Nhiệm Vụ Phụ "Khảo sát Vực Sâu."
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Có thể nhận sau khi hoàn thành Nhiệm Vụ Phụ "Khảo sát Vực Sâu."
 Sự sống có thể bị chế giễu, trở thành cái giá của sự dối trá.</t>
         </is>
       </c>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Có thể nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Dấu Chân Trên Cao Nguyên."
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Có thể nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Dấu Chân Trên Cao Nguyên."
 Vinh quang được tôi luyện thành những tượng đài khổng lồ, thắp lại quyết tâm đã mất từ lâu.</t>
         </is>
       </c>
@@ -8076,7 +8076,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Có thể nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Lời Thì Thầm Của Sóng."
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Có thể nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Lời Thì Thầm Của Sóng."
 Hãy để lời thì thầm vang vọng, xoa dịu trái tim mệt nhoài.</t>
         </is>
       </c>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Lời Thì Thầm Của Sóng".
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Lời Thì Thầm Của Sóng".
 Hãy để lời thì thầm vang vọng, kể về những câu chuyện của ánh sáng và bóng tối.</t>
         </is>
       </c>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Lời Thì Thầm Của Sóng".
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Lời Thì Thầm Của Sóng".
 Hãy để lời thì thầm vang vọng, gửi gắm ước nguyện theo làn gió.</t>
         </is>
       </c>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Có thể nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Lời Thì Thầm Của Sóng."
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Có thể nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Lời Thì Thầm Của Sóng."
 Hãy để lời thì thầm vang vọng, trôi dạt qua mùa hạ bất tận.</t>
         </is>
       </c>
@@ -8539,7 +8539,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Có thể nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Lời Thì Thầm Của Sóng."
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Có thể nhận được sau khi hoàn thành Nhiệm Vụ Phụ "Lời Thì Thầm Của Sóng."
 Hãy để lời thì thầm vang vọng, che giấu quá khứ đã bị lãng quên.</t>
         </is>
       </c>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>"Sự tĩnh lặng của Rừng Bjartr có thể xoa dịu mọi căng thẳng học thuật. Còn ẩm thực địa phương của Roya thì còn làm tốt hơn thế."</t>
+          <t>"Sự tĩnh lặng của Bjartr Woods có thể xoa dịu mọi căng thẳng học thuật. Còn ẩm thực địa phương của Roya thì còn làm tốt hơn thế."</t>
         </is>
       </c>
     </row>
@@ -9199,7 +9199,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;Youth, frozen in blazing expectations.&lt;/color&gt;
+          <t>&lt;color=#c49e55&gt;Tuổi trẻ, đóng băng trong những kỳ vọng rực cháy.&lt;/color&gt;
 Có thể nhận được sau khi bắt đầu Nhiệm Vụ Phụ "Bắt Giữ Ánh Sao".</t>
         </is>
       </c>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;Disaster, frozen in the fear that has yet to die.&lt;/color&gt;
+          <t>&lt;color=#c49e55&gt;Thảm họa, đóng băng trong nỗi sợ chưa chết.&lt;/color&gt;
 Có thể nhận sau khi bắt đầu Nhiệm Vụ Phụ "Bắt Giữ Ánh Sao".</t>
         </is>
       </c>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;Aspiration, frozen in every step that reaches upward.&lt;/color&gt;
+          <t>&lt;color=#c49e55&gt;Khát vọng, đóng băng trong từng bước vươn lên.&lt;/color&gt;
 Có thể nhận sau khi bắt đầu Nhiệm Vụ Phụ "Bắt Giữ Ánh Sao".</t>
         </is>
       </c>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Món quà tri ân đặc biệt dành cho các Rover trên toàn thế giới!</t>
+          <t>Món quà tri ân đặc biệt dành cho các Vận Mệnh Giả trên toàn thế giới!</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Nâng cấp 1 Cộng Hưởng Giả lên Lv. 20</t>
+          <t>Nâng cấp 1 Resonator lên Lv. 20</t>
         </is>
       </c>
     </row>
@@ -10640,7 +10640,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Nâng cấp 1 Cộng Hưởng Giả lên Lv. 30</t>
+          <t>Nâng cấp 1 Resonator lên Lv. 30</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Nâng cấp 3 Cộng Hưởng Giả lên cấp 30</t>
+          <t>Nâng cấp 3 Resonator lên cấp 30</t>
         </is>
       </c>
     </row>
@@ -10900,7 +10900,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Nâng cấp 1 Cộng Hưởng Giả lên Lv. 50</t>
+          <t>Nâng cấp 1 Resonator lên Lv. 50</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Nâng cấp 3 Cộng Hưởng Giả lên cấp 50</t>
+          <t>Nâng cấp 3 Resonator lên cấp 50</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Nâng cấp 2 kỹ năng của 2 Cộng Hưởng Giả lên cấp 3</t>
+          <t>Nâng cấp 2 kỹ năng của 2 Resonator lên cấp 3</t>
         </is>
       </c>
     </row>
@@ -11420,7 +11420,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Nâng cấp 1 Cộng Hưởng Giả lên Lv. 60</t>
+          <t>Nâng cấp 1 Resonator lên Lv. 60</t>
         </is>
       </c>
     </row>
@@ -11615,7 +11615,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Nâng cấp 2 kỹ năng của 3 Cộng Hưởng Giả lên cấp 3</t>
+          <t>Nâng cấp 2 kỹ năng của 3 Resonator lên cấp 3</t>
         </is>
       </c>
     </row>
@@ -11680,7 +11680,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Nâng cấp 1 Cộng Hưởng Giả lên cấp 70</t>
+          <t>Nâng cấp 1 Resonator lên cấp 70</t>
         </is>
       </c>
     </row>
@@ -11940,7 +11940,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Nâng cấp 3 Cộng Hưởng Giả lên cấp 70</t>
+          <t>Nâng cấp 3 Resonator lên cấp 70</t>
         </is>
       </c>
     </row>
@@ -12005,7 +12005,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Nâng cấp 3 kỹ năng của 3 Cộng Hưởng Giả lên cấp 4</t>
+          <t>Nâng cấp 3 kỹ năng của 3 Resonator lên cấp 4</t>
         </is>
       </c>
     </row>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Nâng cấp 1 Cộng Hưởng Giả lên cấp 80</t>
+          <t>Nâng cấp 1 Resonator lên cấp 80</t>
         </is>
       </c>
     </row>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Nâng cấp 3 kỹ năng của 3 Cộng Hưởng Giả lên cấp 6</t>
+          <t>Nâng cấp 3 kỹ năng của 3 Resonator lên cấp 6</t>
         </is>
       </c>
     </row>
@@ -13500,7 +13500,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Cậu NGHĨ NÓ SẼ LÀ {} HẢ?</t>
+          <t>MÀY NGHĨ NÓ SẼ LÀ {} HẢ?</t>
         </is>
       </c>
     </row>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Trên những vách đá cao chót vót vươn lên trời, một con rồng thực sự xuất hiện từ trong mây.</t>
+          <t>Trên những vách đá cao chót vót vươn lên trời, một con rồng đích thực hiện ra từ trong mây.</t>
         </is>
       </c>
     </row>
@@ -16169,7 +16169,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Âm nhạc, kịch nghệ và Tiếng Vang—hãy khám phá mọi điều rực rỡ được dệt nên trong từng ngóc ngách của Rinascita.</t>
+          <t>Âm nhạc, kịch nghệ và Echo—hãy khám phá mọi điều rực rỡ được dệt nên trong từng ngóc ngách của Rinascita.</t>
         </is>
       </c>
     </row>
@@ -16559,7 +16559,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Tất Cả Ra Trận! Vươn Tới Đỉnh Danh Vọng</t>
+          <t>Tất Cả Vào Cuộc! Vươn Tới Đỉnh Danh Vọng</t>
         </is>
       </c>
     </row>
@@ -16754,7 +16754,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Ta muốn được chứng kiến bầu trời bên ngoài bầu trời, chạm tới thế giới bên ngoài thế giới.</t>
+          <t>Tao muốn được chứng kiến bầu trời bên ngoài bầu trời, chạm tới thế giới bên ngoài thế giới.</t>
         </is>
       </c>
     </row>
@@ -24034,7 +24034,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>&lt;color=#e1ac68&gt;{0}/{1}&lt;/color&gt;</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -24099,7 +24099,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>&lt;color=#8f8f8f&gt;{0}/{1}&lt;/color&gt;</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
@@ -24359,7 +24359,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Rank 4 Echo absorption probability increased&lt;/color&gt;</t>
+          <t>&lt;color=Highlight&gt;Xác suất hấp thụ Echo cấp 4 tăng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24489,7 +24489,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Rank 4 Echo absorption probability greatly increased&lt;/color&gt;</t>
+          <t>&lt;color=Highlight&gt;Xác suất hấp thụ Echo cấp 4 tăng mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24619,7 +24619,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Chất lượng hấp thụ cao nhất Hạng 4 → &lt;color=Highlight&gt;Rank 5&lt;/color&gt;</t>
+          <t>Chất lượng hấp thụ cao nhất Hạng 4 → &lt;color=Highlight&gt;Hạng 5&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24749,7 +24749,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Rank 5 Echo absorption probability increased&lt;/color&gt;</t>
+          <t>&lt;color=Highlight&gt;Xác suất hấp thụ Echo cấp 5 tăng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Rank 5 Echo absorption probability greatly increased&lt;/color&gt;</t>
+          <t>&lt;color=Highlight&gt;Xác suất hấp thụ Echo cấp 5 tăng mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -25659,7 +25659,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Tổng cộng dùng 600 Tấm Sóng Âm.</t>
+          <t>Tổng cộng dùng 600 Waveplate Âm.</t>
         </is>
       </c>
     </row>
@@ -27154,7 +27154,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;5-Star Echo is guaranteed&lt;/color&gt;</t>
+          <t>&lt;color=Highlight&gt;Đảm bảo Echo 5 sao&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -27609,7 +27609,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Chất lượng hấp thụ cao nhất Hạng 2 → &lt;color=Highlight&gt;Rank 3&lt;/color&gt;</t>
+          <t>Chất lượng hấp thụ cao nhất Hạng 2 → &lt;color=Highlight&gt;Hạng 3&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -27739,7 +27739,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Rank 3 Echo absorption probability increased&lt;/color&gt;</t>
+          <t>&lt;color=Highlight&gt;Xác suất hấp thụ Echo cấp 3 tăng&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -27804,7 +27804,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Rank 3 Echo absorption probability greatly increased&lt;/color&gt;</t>
+          <t>&lt;color=Highlight&gt;Xác suất hấp thụ Echo cấp 3 tăng mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -27869,7 +27869,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Chất lượng hấp thụ cao nhất Hạng 3 → &lt;color=Highlight&gt;Rank 4&lt;/color&gt;</t>
+          <t>Chất lượng hấp thụ cao nhất Hạng 3 → &lt;color=Highlight&gt;Hạng 4&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -28649,7 +28649,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Người ta đồn Mahe ở Kim Châu có bí quyết nấu Súp Trong độc nhất vô nhị. Sao không thử hỏi ông ấy xem?</t>
+          <t>Người ta đồn Mahe ở Jinzhou có bí quyết nấu Súp Trong độc nhất vô nhị. Sao không thử hỏi ông ấy xem?</t>
         </is>
       </c>
     </row>
@@ -28779,7 +28779,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Nghe nói chú Lý ở Kim Châu có bí quyết nấu món Súp Trong độc đáo lắm. Sao cậu không thử hỏi chú ấy xem?</t>
+          <t>Nghe nói chú Lý ở Jinzhou có bí quyết nấu món Súp Trong độc đáo lắm. Sao cậu không thử hỏi chú ấy xem?</t>
         </is>
       </c>
     </row>
@@ -28909,7 +28909,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Người ta đồn Koko ở Kim Châu có bí quyết nấu Canh Thanh độc nhất vô nhị. Sao cậu không thử hỏi cô ấy nhỉ?</t>
+          <t>Người ta đồn Koko ở Jinzhou có bí quyết nấu Canh Thanh độc nhất vô nhị. Sao cậu không thử hỏi cô ấy nhỉ?</t>
         </is>
       </c>
     </row>
@@ -29039,7 +29039,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Nghe nói chú Vi ở Kim Châu am hiểu cách làm nước sốt kho độc đáo lắm. Sao không thử hỏi chú ấy nhỉ?</t>
+          <t>Nghe nói chú Vi ở Jinzhou am hiểu cách làm nước sốt kho độc đáo lắm. Sao không thử hỏi chú ấy nhỉ?</t>
         </is>
       </c>
     </row>
@@ -29169,7 +29169,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Nghe nói Cảm Huyết ở Kim Châu có bí quyết riêng về cách nấu Nước Sốt Rim. Sao cậu không thử hỏi cô ấy xem?</t>
+          <t>Nghe nói Cảm Huyết ở Jinzhou có bí quyết riêng về cách nấu Nước Sốt Rim. Sao cậu không thử hỏi cô ấy xem?</t>
         </is>
       </c>
     </row>
@@ -30014,7 +30014,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>DNS resolution error. Error code:</t>
+          <t>Lỗi phân giải DNS. Mã lỗi:</t>
         </is>
       </c>
     </row>
@@ -30079,7 +30079,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Web access error. Error code:</t>
+          <t>Lỗi truy cập mạng. Mã lỗi:</t>
         </is>
       </c>
     </row>
@@ -30209,7 +30209,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Nhấn nút để bắt đầu test mạng.</t>
+          <t>Nhấn nút để bắt đầu kiểm tra mạng.</t>
         </is>
       </c>
     </row>
@@ -30404,7 +30404,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Đang test mạng. Nhấn lại để dừng test và thoát trang này.</t>
+          <t>Đang kiểm tra mạng. Nhấn lại để dừng kiểm tra và thoát khỏi trang này.</t>
         </is>
       </c>
     </row>
@@ -30535,7 +30535,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Từ đây, chiêm ngưỡng phản chiếu kỳ vĩ.
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Từ đây, chiêm ngưỡng phản chiếu kỳ vĩ.
 Có thể nhận sau khi tiếp tục Nhiệm vụ Phụ "Dấu Chân Avinoleum".</t>
         </is>
       </c>
@@ -30667,7 +30667,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Từ đây, tìm kiếm ký ức còn vương vấn của bữa tiệc.
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Từ đây, tìm kiếm ký ức còn vương vấn của bữa tiệc.
 Có thể nhận sau khi hoàn thành Nhiệm Vụ Phụ "Dấu chân Avinoleum."</t>
         </is>
       </c>
@@ -30799,7 +30799,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Từ đây, bước vào vòng xoáy của suy tưởng.
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Từ đây, bước vào vòng xoáy của suy tưởng.
 Có thể nhận sau khi hoàn thành Nhiệm Vụ Phụ "Dấu chân Avinoleum."</t>
         </is>
       </c>
@@ -30931,7 +30931,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Từ đây, hồi tưởng lại thiên đường đã lãng quên.
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Từ đây, hồi tưởng lại thiên đường đã lãng quên.
 Có thể nhận sau khi hoàn thành Nhiệm Vụ Phụ "Dấu chân Avinoleum."</t>
         </is>
       </c>
@@ -31063,7 +31063,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Từ đây, chứng kiến hoàng hôn của niềm tin.
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Từ đây, chứng kiến hoàng hôn của niềm tin.
 Có thể nhận sau khi hoàn thành Nhiệm Vụ Phụ "Dấu chân Avinoleum."</t>
         </is>
       </c>
@@ -31195,7 +31195,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Từ đây, giải thoát những linh hồn lạc lối.
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Từ đây, giải thoát những linh hồn lạc lối.
 Có thể nhận sau khi hoàn thành Nhiệm Vụ Khám Phá "Nếu Sao Băng Rực Cháy."</t>
         </is>
       </c>
@@ -31261,7 +31261,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; "Xin phép được giới thiệu bản thân một cách chính thức. Ta là Jinhsi. Rất vui được gặp cậu, Rover."</t>
+          <t>&lt;color=#c49e55&gt;[Manh Mối]&lt;/color&gt; "Xin phép được giới thiệu bản thân một cách chính thức. Ta là Jinhsi. Rất vui được gặp cậu, Vận Mệnh Giả."</t>
         </is>
       </c>
     </row>
@@ -31326,7 +31326,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; "Ta hiểu rồi. Có lẽ vì thế... thật khó lòng rời bỏ thế giới tươi đẹp này."</t>
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; "Ta hiểu rồi. Có lẽ vì thế... thật khó lòng rời bỏ thế giới tươi đẹp này."</t>
         </is>
       </c>
     </row>
@@ -31391,7 +31391,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; "Ngươi nên đi thôi. Hẹn gặp lại lần sau."</t>
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; "Ngươi nên đi thôi. Hẹn gặp lại lần sau."</t>
         </is>
       </c>
     </row>
@@ -32367,7 +32367,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Nhận được sau khi bắt đầu Nhiệm Vụ Phụ "Khám Phá Anh Hùng Xưa".
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Nhận được sau khi bắt đầu Nhiệm Vụ Phụ "Khám Phá Anh Hùng Xưa".
 Diện mạo của Septimont kiên định và bất khuất.</t>
         </is>
       </c>
@@ -32434,7 +32434,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Nhận được sau khi bắt đầu Nhiệm Vụ Phụ "Khám Phá Anh Hùng Xưa".
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Nhận được sau khi bắt đầu Nhiệm Vụ Phụ "Khám Phá Anh Hùng Xưa".
 Trụ cột của Septimont vững chãi, sừng sững.</t>
         </is>
       </c>
@@ -32566,7 +32566,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Nhận được sau khi bắt đầu Nhiệm Vụ Phụ "Khám Phá Anh Hùng Xưa".
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Nhận được sau khi bắt đầu Nhiệm Vụ Phụ "Khám Phá Anh Hùng Xưa".
 Vết thương của Septimont hoang tàn, tiêu điều.</t>
         </is>
       </c>
@@ -32633,7 +32633,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Nhận được sau khi bắt đầu Nhiệm Vụ Phụ "Khám Phá Anh Hùng Xưa".
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Nhận được sau khi bắt đầu Nhiệm Vụ Phụ "Khám Phá Anh Hùng Xưa".
 Di sản của Septimont vươn cao, hùng vĩ.</t>
         </is>
       </c>
@@ -32765,7 +32765,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Nhận được sau khi bắt đầu Nhiệm Vụ Phụ "Khám Phá Anh Hùng Xưa".
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Nhận được sau khi bắt đầu Nhiệm Vụ Phụ "Khám Phá Anh Hùng Xưa".
 Tinh thần của Septimont hào sảng, vang dội.</t>
         </is>
       </c>
@@ -32832,7 +32832,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Clue]&lt;/color&gt; Nhận được sau khi bắt đầu Nhiệm Vụ Phụ "Khám Phá Anh Hùng Xưa".
+          <t>&lt;color=#c49e55&gt;[Manh mối]&lt;/color&gt; Nhận được sau khi bắt đầu Nhiệm Vụ Phụ "Khám Phá Anh Hùng Xưa".
 Vinh quang của Septimont rực rỡ và vĩnh cửu.</t>
         </is>
       </c>
@@ -32898,7 +32898,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Completed: {0}/{1}</t>
+          <t>Hoàn thành: {0}/{1}</t>
         </is>
       </c>
     </row>
